--- a/backend/data/Plantilla Fondo de Tiempo CIS 2023_WCHAO.xlsx
+++ b/backend/data/Plantilla Fondo de Tiempo CIS 2023_WCHAO.xlsx
@@ -1,50 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DISCO SEAGATE\3 SECTOR PUBLICO\U.A.B.J.B\ING. SISTEMAS _ UABJB\3. ALGEBRA LINEAL\PROGRAMA ANALITICO ALGEBRA LINEAL 1.2023\Guias Nuevas 2021\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18396E35-07F9-C54D-98A1-567074238803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="718" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="DOCENCIA 2021" sheetId="3" r:id="rId1"/>
-    <sheet name="PLAN ASIGNATURA DOCENCIA" sheetId="2" r:id="rId2"/>
-    <sheet name="TIEMPO COMPLETO" sheetId="5" r:id="rId3"/>
-    <sheet name="PLAN Tiempo Completo" sheetId="6" r:id="rId4"/>
-    <sheet name="Plan de Estudios CIS" sheetId="4" r:id="rId5"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TIEMPO COMPLETO'!$A$3:$AO$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PLAN ASIGNATURA DOCENCIA'!$A$1:$F$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'PLAN Tiempo Completo'!$A$1:$F$49</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PLAN ASIGNATURA DOCENCIA'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'PLAN Tiempo Completo'!$1:$3</definedName>
-  </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="462">
@@ -20198,691 +20151,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="39.4140625" customWidth="1"/>
-    <col min="3" max="3" width="26.90234375" customWidth="1"/>
-    <col min="4" max="4" width="34.03125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="C1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>454</v>
-      </c>
-      <c r="C2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="195" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="174" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="174" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="175" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="195" t="s">
-        <v>450</v>
-      </c>
-      <c r="F3" s="195" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="215" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="191" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="186" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="196" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="187"/>
-      <c r="F4" s="197">
-        <v>44935</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="216"/>
-      <c r="B5" s="170" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="171" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="176" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-    </row>
-    <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="216"/>
-      <c r="B6" s="170" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="171" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="176" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-    </row>
-    <row r="7" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="216"/>
-      <c r="B7" s="170" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="171" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="177"/>
-      <c r="E7" s="179"/>
-      <c r="F7" s="179"/>
-    </row>
-    <row r="8" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="216"/>
-      <c r="B8" s="170" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="171" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="177"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
-    </row>
-    <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="216"/>
-      <c r="B9" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="172"/>
-      <c r="D9" s="177"/>
-      <c r="E9" s="179"/>
-      <c r="F9" s="179"/>
-    </row>
-    <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="172"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="179"/>
-      <c r="F10" s="179"/>
-    </row>
-    <row r="11" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="217"/>
-      <c r="B11" s="192" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="193"/>
-      <c r="D11" s="198"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="180"/>
-    </row>
-    <row r="12" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="215" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="191" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="186" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="181" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-    </row>
-    <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="216"/>
-      <c r="B13" s="170" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="171" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="182" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="179">
-        <v>150</v>
-      </c>
-      <c r="F13" s="179"/>
-    </row>
-    <row r="14" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="216"/>
-      <c r="B14" s="170" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="171" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="182" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="179">
-        <v>40</v>
-      </c>
-      <c r="F14" s="179"/>
-    </row>
-    <row r="15" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="216"/>
-      <c r="B15" s="170" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="171" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="182" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="179">
-        <v>80</v>
-      </c>
-      <c r="F15" s="179"/>
-    </row>
-    <row r="16" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="216"/>
-      <c r="B16" s="170" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="171" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="178"/>
-      <c r="E16" s="179">
-        <v>40</v>
-      </c>
-      <c r="F16" s="179"/>
-    </row>
-    <row r="17" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="216"/>
-      <c r="B17" s="170" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="172"/>
-      <c r="D17" s="178"/>
-      <c r="E17" s="179">
-        <v>40</v>
-      </c>
-      <c r="F17" s="179"/>
-    </row>
-    <row r="18" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="217"/>
-      <c r="B18" s="188"/>
-      <c r="C18" s="193"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="180"/>
-    </row>
-    <row r="19" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="218" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="191" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="186" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="218" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="187">
-        <v>40</v>
-      </c>
-      <c r="F19" s="187"/>
-    </row>
-    <row r="20" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="219"/>
-      <c r="B20" s="170" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="171" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="219"/>
-      <c r="E20" s="179">
-        <v>60</v>
-      </c>
-      <c r="F20" s="179"/>
-    </row>
-    <row r="21" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="219"/>
-      <c r="B21" s="170" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="171" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="219"/>
-      <c r="E21" s="179">
-        <v>60</v>
-      </c>
-      <c r="F21" s="179"/>
-    </row>
-    <row r="22" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="219"/>
-      <c r="B22" s="170" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="171" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="219"/>
-      <c r="E22" s="179">
-        <v>20</v>
-      </c>
-      <c r="F22" s="179"/>
-    </row>
-    <row r="23" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="219"/>
-      <c r="B23" s="170" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="171" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="219"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="179"/>
-    </row>
-    <row r="24" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="219"/>
-      <c r="B24" s="170" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="172"/>
-      <c r="D24" s="219"/>
-      <c r="E24" s="179">
-        <v>60</v>
-      </c>
-      <c r="F24" s="179"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="219"/>
-      <c r="B25" s="170" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="172"/>
-      <c r="D25" s="219"/>
-      <c r="E25" s="179"/>
-      <c r="F25" s="179"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="220"/>
-      <c r="B26" s="188"/>
-      <c r="C26" s="193"/>
-      <c r="D26" s="220"/>
-      <c r="E26" s="180"/>
-      <c r="F26" s="180"/>
-    </row>
-    <row r="27" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="215" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="186" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="218" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="187">
-        <v>20</v>
-      </c>
-      <c r="F27" s="187"/>
-    </row>
-    <row r="28" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="216"/>
-      <c r="B28" s="170" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="171" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="219"/>
-      <c r="E28" s="179">
-        <v>40</v>
-      </c>
-      <c r="F28" s="179"/>
-    </row>
-    <row r="29" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="216"/>
-      <c r="B29" s="170" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="171" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="219"/>
-      <c r="E29" s="179">
-        <v>60</v>
-      </c>
-      <c r="F29" s="179"/>
-    </row>
-    <row r="30" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="216"/>
-      <c r="B30" s="170" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="171" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="219"/>
-      <c r="E30" s="179">
-        <v>10</v>
-      </c>
-      <c r="F30" s="179"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="216"/>
-      <c r="B31" s="170" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="171" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="219"/>
-      <c r="E31" s="179">
-        <v>10</v>
-      </c>
-      <c r="F31" s="179"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="216"/>
-      <c r="B32" s="170" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="219"/>
-      <c r="E32" s="179">
-        <v>10</v>
-      </c>
-      <c r="F32" s="179"/>
-    </row>
-    <row r="33" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="217"/>
-      <c r="B33" s="192" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="193"/>
-      <c r="D33" s="220"/>
-      <c r="E33" s="180">
-        <v>10</v>
-      </c>
-      <c r="F33" s="180"/>
-    </row>
-    <row r="34" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="215" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="221" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="186" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="187">
-        <v>38</v>
-      </c>
-      <c r="F34" s="187"/>
-    </row>
-    <row r="35" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="216"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="171" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="219"/>
-      <c r="E35" s="179">
-        <v>40</v>
-      </c>
-      <c r="F35" s="179"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="216"/>
-      <c r="B36" s="222"/>
-      <c r="C36" s="171" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="219"/>
-      <c r="E36" s="179">
-        <v>50</v>
-      </c>
-      <c r="F36" s="179"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="217"/>
-      <c r="B37" s="223"/>
-      <c r="C37" s="189" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="220"/>
-      <c r="E37" s="180">
-        <v>100</v>
-      </c>
-      <c r="F37" s="180"/>
-    </row>
-    <row r="38" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="215" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="185" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="186" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="218" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="187">
-        <v>48</v>
-      </c>
-      <c r="F38" s="187"/>
-    </row>
-    <row r="39" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="216"/>
-      <c r="B39" s="183" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="171" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="219"/>
-      <c r="E39" s="179">
-        <v>60</v>
-      </c>
-      <c r="F39" s="179"/>
-    </row>
-    <row r="40" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="216"/>
-      <c r="B40" s="183" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="171" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="219"/>
-      <c r="E40" s="179">
-        <v>60</v>
-      </c>
-      <c r="F40" s="179"/>
-    </row>
-    <row r="41" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="216"/>
-      <c r="B41" s="183" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="171" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="219"/>
-      <c r="E41" s="179"/>
-      <c r="F41" s="179"/>
-    </row>
-    <row r="42" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="216"/>
-      <c r="B42" s="183"/>
-      <c r="C42" s="171" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42" s="219"/>
-      <c r="E42" s="179">
-        <v>100</v>
-      </c>
-      <c r="F42" s="179"/>
-    </row>
-    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="216"/>
-      <c r="B43" s="173"/>
-      <c r="C43" s="171" t="s">
-        <v>60</v>
-      </c>
-      <c r="D43" s="219"/>
-      <c r="E43" s="179">
-        <v>120</v>
-      </c>
-      <c r="F43" s="179"/>
-    </row>
-    <row r="44" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="217"/>
-      <c r="B44" s="190"/>
-      <c r="C44" s="189"/>
-      <c r="D44" s="220"/>
-      <c r="E44" s="180"/>
-      <c r="F44" s="180"/>
-    </row>
-    <row r="45" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="215" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" s="185" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="186" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="218" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="187">
-        <v>50</v>
-      </c>
-      <c r="F45" s="187"/>
-    </row>
-    <row r="46" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="216"/>
-      <c r="B46" s="183" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="171" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="219"/>
-      <c r="E46" s="179">
-        <v>50</v>
-      </c>
-      <c r="F46" s="179"/>
-    </row>
-    <row r="47" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="216"/>
-      <c r="B47" s="183" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="171" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="219"/>
-      <c r="E47" s="179">
-        <v>30</v>
-      </c>
-      <c r="F47" s="179"/>
-    </row>
-    <row r="48" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="217"/>
-      <c r="B48" s="188"/>
-      <c r="C48" s="189" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="220"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="180"/>
-    </row>
-    <row r="49" spans="4:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="184" t="s">
-        <v>456</v>
-      </c>
-      <c r="E49" s="199">
-        <f>SUM(E4:E48)</f>
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="50" spans="4:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D50" s="9"/>
-    </row>
-    <row r="51" spans="4:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="4:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="4:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A19:A26"/>
-    <mergeCell ref="D19:D26"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="D27:D33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="D38:D44"/>
-  </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="90" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;G</oddHeader>
-  </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AD106"/>
